--- a/files/lbo-acquisition-model.xlsx
+++ b/files/lbo-acquisition-model.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kieranoconnell/Desktop/portfolio - Main/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kieranoconnell/Desktop/portfolio - Main/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F51B81C1-E6B2-F946-B283-40892F315B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19780" activeTab="6" xr2:uid="{8336B80D-68BD-214C-A3D1-13CFBDD0A36D}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19780" xr2:uid="{8336B80D-68BD-214C-A3D1-13CFBDD0A36D}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="9" r:id="rId1"/>
@@ -667,6 +667,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -686,15 +695,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1705,53 +1705,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
     </row>
     <row r="2" spans="1:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C3" s="39">
+      <c r="C3" s="42">
         <f ca="1">TODAY()</f>
-        <v>46102</v>
-      </c>
-      <c r="D3" s="39"/>
+        <v>46103</v>
+      </c>
+      <c r="D3" s="42"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="43" t="s">
         <v>124</v>
       </c>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="37"/>
-      <c r="B5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
+      <c r="A5" s="40"/>
+      <c r="B5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="37"/>
-      <c r="B9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
+      <c r="A9" s="40"/>
+      <c r="B9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="36"/>
@@ -1811,10 +1811,10 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="41"/>
+      <c r="B3" s="44"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
@@ -1857,10 +1857,10 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="41"/>
+      <c r="B10" s="44"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
@@ -1910,14 +1910,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="D1" s="43" t="s">
+      <c r="B1" s="45"/>
+      <c r="D1" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="43"/>
+      <c r="E1" s="46"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -1981,10 +1981,10 @@
       <c r="B6" s="5">
         <v>5</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="43"/>
+      <c r="E6" s="46"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D7" s="2" t="s">
@@ -1996,10 +1996,10 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="42"/>
+      <c r="B8" s="45"/>
       <c r="D8" s="2" t="s">
         <v>37</v>
       </c>
@@ -2091,10 +2091,10 @@
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="42" t="s">
+      <c r="A18" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="42"/>
+      <c r="B18" s="45"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
@@ -2137,10 +2137,10 @@
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="42" t="s">
+      <c r="A25" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="42"/>
+      <c r="B25" s="45"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
@@ -2190,10 +2190,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="44"/>
+      <c r="F1" s="38"/>
     </row>
     <row r="2" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B2" s="11" t="s">
@@ -2722,11 +2722,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B2" s="15" t="s">
@@ -2938,11 +2938,11 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B13" s="15" t="s">
@@ -3210,11 +3210,11 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C26" s="37" t="s">
+      <c r="C26" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="D26" s="37"/>
-      <c r="E26" s="37"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B27" s="15" t="s">
@@ -3457,15 +3457,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
@@ -3614,10 +3614,10 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="44" t="s">
+      <c r="A18" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="B18" s="44"/>
+      <c r="B18" s="38"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="24" t="s">
@@ -3670,10 +3670,10 @@
       <c r="E23" s="28"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="46" t="s">
+      <c r="A24" s="39" t="s">
         <v>119</v>
       </c>
-      <c r="B24" s="46"/>
+      <c r="B24" s="39"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="32" t="s">
